--- a/AAII_Financials/Yearly/NGL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NGL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
   <si>
     <t>NGL</t>
   </si>
@@ -1608,7 +1608,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-142300</v>
+        <v>-405600</v>
       </c>
       <c r="E27" s="3">
         <v>-78900</v>
@@ -2267,7 +2267,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>661500</v>
+        <v>664800</v>
       </c>
       <c r="E43" s="3">
         <v>583200</v>
@@ -2368,8 +2368,8 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>5800</v>
       </c>
       <c r="E45" s="3">
         <v>244200</v>
@@ -2573,7 +2573,7 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1156600</v>
+        <v>1143000</v>
       </c>
       <c r="E49" s="3">
         <v>1433600</v>
@@ -2972,7 +2972,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>44900</v>
+        <v>47600</v>
       </c>
       <c r="E58" s="3">
         <v>36700</v>
@@ -3023,7 +3023,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>15200</v>
+        <v>61700</v>
       </c>
       <c r="E59" s="3">
         <v>127100</v>
@@ -3125,10 +3125,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3305300</v>
+        <v>3309800</v>
       </c>
       <c r="E61" s="3">
-        <v>3047000</v>
+        <v>3046900</v>
       </c>
       <c r="F61" s="3">
         <v>2914400</v>
@@ -3176,7 +3176,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>137000</v>
+        <v>103900</v>
       </c>
       <c r="E62" s="3">
         <v>96000</v>
@@ -4090,7 +4090,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>268700</v>
+        <v>200200</v>
       </c>
       <c r="E83" s="3">
         <v>198900</v>
